--- a/data_lake/datos_diarios_preliminares/dt=2026-09-13/temperaturamed.xlsx
+++ b/data_lake/datos_diarios_preliminares/dt=2026-09-13/temperaturamed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\01. Tematicas\05. Datos Hidrometeorologicos\01. Productos\02.Tablas\temporales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC6EB18-77E5-4720-8C28-DC07DA80DC6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2139E381-D1BF-4F9E-9E8C-D22A3C141FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="729" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6353,8 +6353,8 @@
     <col min="43" max="43" width="20.7109375" style="53" customWidth="1"/>
     <col min="44" max="44" width="24.85546875" style="69" customWidth="1"/>
     <col min="45" max="45" width="13.28515625" style="70" bestFit="1" customWidth="1"/>
-    <col min="46" max="161" width="32.42578125" style="50" customWidth="1"/>
-    <col min="162" max="16384" width="32.42578125" style="50"/>
+    <col min="46" max="162" width="32.42578125" style="50" customWidth="1"/>
+    <col min="163" max="16384" width="32.42578125" style="50"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.2">
@@ -6670,7 +6670,9 @@
       <c r="U5" s="56">
         <v>30.4</v>
       </c>
-      <c r="V5" s="56"/>
+      <c r="V5" s="56">
+        <v>29.9</v>
+      </c>
       <c r="W5" s="56"/>
       <c r="X5" s="56"/>
       <c r="Y5" s="56"/>
@@ -6692,7 +6694,7 @@
       <c r="AO5" s="56"/>
       <c r="AP5" s="58">
         <f t="shared" ref="AP5:AP68" si="0">COUNTIF(K5:AO5,"&gt;0")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ5" s="71" t="str">
         <f t="shared" ref="AQ5:AQ68" si="1">IF(AP5&gt;14,AVERAGE(K5:AO5),"")</f>
@@ -6771,7 +6773,9 @@
       <c r="U6" s="56">
         <v>29.6</v>
       </c>
-      <c r="V6" s="56"/>
+      <c r="V6" s="56">
+        <v>30.1</v>
+      </c>
       <c r="W6" s="56"/>
       <c r="X6" s="56"/>
       <c r="Y6" s="56"/>
@@ -6793,7 +6797,7 @@
       <c r="AO6" s="56"/>
       <c r="AP6" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ6" s="71" t="str">
         <f t="shared" si="1"/>
@@ -6872,7 +6876,9 @@
       <c r="U7" s="56">
         <v>31.5</v>
       </c>
-      <c r="V7" s="56"/>
+      <c r="V7" s="56">
+        <v>30.2</v>
+      </c>
       <c r="W7" s="56"/>
       <c r="X7" s="56"/>
       <c r="Y7" s="56"/>
@@ -6894,7 +6900,7 @@
       <c r="AO7" s="56"/>
       <c r="AP7" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ7" s="71" t="str">
         <f t="shared" si="1"/>
@@ -6973,7 +6979,9 @@
       <c r="U8" s="56">
         <v>30.3</v>
       </c>
-      <c r="V8" s="56"/>
+      <c r="V8" s="56">
+        <v>30.6</v>
+      </c>
       <c r="W8" s="56"/>
       <c r="X8" s="56"/>
       <c r="Y8" s="56"/>
@@ -6995,7 +7003,7 @@
       <c r="AO8" s="56"/>
       <c r="AP8" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ8" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7074,7 +7082,9 @@
       <c r="U9" s="56">
         <v>30.1</v>
       </c>
-      <c r="V9" s="56"/>
+      <c r="V9" s="56">
+        <v>30.1</v>
+      </c>
       <c r="W9" s="56"/>
       <c r="X9" s="56"/>
       <c r="Y9" s="56"/>
@@ -7096,7 +7106,7 @@
       <c r="AO9" s="56"/>
       <c r="AP9" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ9" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7175,7 +7185,9 @@
       <c r="U10" s="56">
         <v>33.200000000000003</v>
       </c>
-      <c r="V10" s="56"/>
+      <c r="V10" s="56">
+        <v>32.9</v>
+      </c>
       <c r="W10" s="56"/>
       <c r="X10" s="56"/>
       <c r="Y10" s="56"/>
@@ -7197,7 +7209,7 @@
       <c r="AO10" s="56"/>
       <c r="AP10" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ10" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7276,7 +7288,9 @@
       <c r="U11" s="56">
         <v>32.9</v>
       </c>
-      <c r="V11" s="56"/>
+      <c r="V11" s="56">
+        <v>32.9</v>
+      </c>
       <c r="W11" s="56"/>
       <c r="X11" s="56"/>
       <c r="Y11" s="56"/>
@@ -7298,7 +7312,7 @@
       <c r="AO11" s="56"/>
       <c r="AP11" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ11" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7377,7 +7391,9 @@
       <c r="U12" s="56">
         <v>28.1</v>
       </c>
-      <c r="V12" s="56"/>
+      <c r="V12" s="56">
+        <v>30.2</v>
+      </c>
       <c r="W12" s="56"/>
       <c r="X12" s="56"/>
       <c r="Y12" s="56"/>
@@ -7399,7 +7415,7 @@
       <c r="AO12" s="56"/>
       <c r="AP12" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ12" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7478,7 +7494,9 @@
       <c r="U13" s="56">
         <v>28.5</v>
       </c>
-      <c r="V13" s="56"/>
+      <c r="V13" s="56">
+        <v>31.9</v>
+      </c>
       <c r="W13" s="56"/>
       <c r="X13" s="56"/>
       <c r="Y13" s="56"/>
@@ -7500,7 +7518,7 @@
       <c r="AO13" s="56"/>
       <c r="AP13" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ13" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7579,7 +7597,9 @@
       <c r="U14" s="56">
         <v>23.6</v>
       </c>
-      <c r="V14" s="56"/>
+      <c r="V14" s="56">
+        <v>24.6</v>
+      </c>
       <c r="W14" s="56"/>
       <c r="X14" s="56"/>
       <c r="Y14" s="56"/>
@@ -7601,7 +7621,7 @@
       <c r="AO14" s="56"/>
       <c r="AP14" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ14" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7680,7 +7700,9 @@
       <c r="U15" s="56">
         <v>30.5</v>
       </c>
-      <c r="V15" s="56"/>
+      <c r="V15" s="56">
+        <v>31.8</v>
+      </c>
       <c r="W15" s="56"/>
       <c r="X15" s="56"/>
       <c r="Y15" s="56"/>
@@ -7702,7 +7724,7 @@
       <c r="AO15" s="56"/>
       <c r="AP15" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ15" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7781,7 +7803,9 @@
       <c r="U16" s="56">
         <v>26.8</v>
       </c>
-      <c r="V16" s="56"/>
+      <c r="V16" s="56">
+        <v>28.5</v>
+      </c>
       <c r="W16" s="56"/>
       <c r="X16" s="56"/>
       <c r="Y16" s="56"/>
@@ -7803,7 +7827,7 @@
       <c r="AO16" s="56"/>
       <c r="AP16" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ16" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7882,7 +7906,9 @@
       <c r="U17" s="56">
         <v>23.8</v>
       </c>
-      <c r="V17" s="56"/>
+      <c r="V17" s="56">
+        <v>26.6</v>
+      </c>
       <c r="W17" s="56"/>
       <c r="X17" s="56"/>
       <c r="Y17" s="56"/>
@@ -7904,7 +7930,7 @@
       <c r="AO17" s="56"/>
       <c r="AP17" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ17" s="71" t="str">
         <f t="shared" si="1"/>
@@ -7983,7 +8009,9 @@
       <c r="U18" s="56">
         <v>20</v>
       </c>
-      <c r="V18" s="56"/>
+      <c r="V18" s="56">
+        <v>19.8</v>
+      </c>
       <c r="W18" s="56"/>
       <c r="X18" s="56"/>
       <c r="Y18" s="56"/>
@@ -8005,7 +8033,7 @@
       <c r="AO18" s="56"/>
       <c r="AP18" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ18" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8084,7 +8112,9 @@
       <c r="U19" s="56">
         <v>23.2</v>
       </c>
-      <c r="V19" s="56"/>
+      <c r="V19" s="56">
+        <v>24.2</v>
+      </c>
       <c r="W19" s="56"/>
       <c r="X19" s="56"/>
       <c r="Y19" s="56"/>
@@ -8106,7 +8136,7 @@
       <c r="AO19" s="56"/>
       <c r="AP19" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ19" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8185,7 +8215,9 @@
       <c r="U20" s="56">
         <v>24</v>
       </c>
-      <c r="V20" s="56"/>
+      <c r="V20" s="56">
+        <v>25.3</v>
+      </c>
       <c r="W20" s="56"/>
       <c r="X20" s="56"/>
       <c r="Y20" s="56"/>
@@ -8207,7 +8239,7 @@
       <c r="AO20" s="56"/>
       <c r="AP20" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ20" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8286,7 +8318,9 @@
       <c r="U21" s="56">
         <v>27.8</v>
       </c>
-      <c r="V21" s="56"/>
+      <c r="V21" s="56">
+        <v>29.1</v>
+      </c>
       <c r="W21" s="56"/>
       <c r="X21" s="56"/>
       <c r="Y21" s="56"/>
@@ -8308,7 +8342,7 @@
       <c r="AO21" s="56"/>
       <c r="AP21" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ21" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8387,7 +8421,9 @@
       <c r="U22" s="56">
         <v>16</v>
       </c>
-      <c r="V22" s="56"/>
+      <c r="V22" s="56">
+        <v>16.2</v>
+      </c>
       <c r="W22" s="56"/>
       <c r="X22" s="56"/>
       <c r="Y22" s="56"/>
@@ -8409,7 +8445,7 @@
       <c r="AO22" s="56"/>
       <c r="AP22" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ22" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8488,7 +8524,9 @@
       <c r="U23" s="56">
         <v>26.7</v>
       </c>
-      <c r="V23" s="56"/>
+      <c r="V23" s="56">
+        <v>26.9</v>
+      </c>
       <c r="W23" s="56"/>
       <c r="X23" s="56"/>
       <c r="Y23" s="56"/>
@@ -8510,7 +8548,7 @@
       <c r="AO23" s="56"/>
       <c r="AP23" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ23" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8589,7 +8627,9 @@
       <c r="U24" s="56">
         <v>30.6</v>
       </c>
-      <c r="V24" s="56"/>
+      <c r="V24" s="56">
+        <v>30.8</v>
+      </c>
       <c r="W24" s="56"/>
       <c r="X24" s="56"/>
       <c r="Y24" s="56"/>
@@ -8611,7 +8651,7 @@
       <c r="AO24" s="56"/>
       <c r="AP24" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ24" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8690,7 +8730,9 @@
       <c r="U25" s="56">
         <v>22.9</v>
       </c>
-      <c r="V25" s="56"/>
+      <c r="V25" s="56">
+        <v>23.2</v>
+      </c>
       <c r="W25" s="56"/>
       <c r="X25" s="56"/>
       <c r="Y25" s="56"/>
@@ -8712,7 +8754,7 @@
       <c r="AO25" s="56"/>
       <c r="AP25" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ25" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8791,7 +8833,9 @@
       <c r="U26" s="56">
         <v>12.1</v>
       </c>
-      <c r="V26" s="56"/>
+      <c r="V26" s="56">
+        <v>11</v>
+      </c>
       <c r="W26" s="56"/>
       <c r="X26" s="56"/>
       <c r="Y26" s="56"/>
@@ -8813,7 +8857,7 @@
       <c r="AO26" s="56"/>
       <c r="AP26" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ26" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8892,7 +8936,9 @@
       <c r="U27" s="56">
         <v>26.4</v>
       </c>
-      <c r="V27" s="56"/>
+      <c r="V27" s="56">
+        <v>29.9</v>
+      </c>
       <c r="W27" s="56"/>
       <c r="X27" s="56"/>
       <c r="Y27" s="56"/>
@@ -8914,7 +8960,7 @@
       <c r="AO27" s="56"/>
       <c r="AP27" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ27" s="71" t="str">
         <f t="shared" si="1"/>
@@ -8991,7 +9037,9 @@
       <c r="U28" s="56">
         <v>28.9</v>
       </c>
-      <c r="V28" s="56"/>
+      <c r="V28" s="56">
+        <v>28.3</v>
+      </c>
       <c r="W28" s="56"/>
       <c r="X28" s="56"/>
       <c r="Y28" s="56"/>
@@ -9013,7 +9061,7 @@
       <c r="AO28" s="56"/>
       <c r="AP28" s="58">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ28" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9092,7 +9140,9 @@
       <c r="U29" s="56">
         <v>30.1</v>
       </c>
-      <c r="V29" s="56"/>
+      <c r="V29" s="56">
+        <v>28.9</v>
+      </c>
       <c r="W29" s="56"/>
       <c r="X29" s="56"/>
       <c r="Y29" s="56"/>
@@ -9114,7 +9164,7 @@
       <c r="AO29" s="56"/>
       <c r="AP29" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ29" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9193,7 +9243,9 @@
       <c r="U30" s="56">
         <v>25.9</v>
       </c>
-      <c r="V30" s="56"/>
+      <c r="V30" s="56">
+        <v>26.6</v>
+      </c>
       <c r="W30" s="56"/>
       <c r="X30" s="56"/>
       <c r="Y30" s="56"/>
@@ -9215,7 +9267,7 @@
       <c r="AO30" s="56"/>
       <c r="AP30" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ30" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9294,7 +9346,9 @@
       <c r="U31" s="98">
         <v>28.1</v>
       </c>
-      <c r="V31" s="98"/>
+      <c r="V31" s="98">
+        <v>27.6</v>
+      </c>
       <c r="W31" s="98"/>
       <c r="X31" s="98"/>
       <c r="Y31" s="98"/>
@@ -9316,7 +9370,7 @@
       <c r="AO31" s="98"/>
       <c r="AP31" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ31" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9395,7 +9449,9 @@
       <c r="U32" s="56">
         <v>19.533333333333331</v>
       </c>
-      <c r="V32" s="56"/>
+      <c r="V32" s="56">
+        <v>19.733333333333331</v>
+      </c>
       <c r="W32" s="56"/>
       <c r="X32" s="56"/>
       <c r="Y32" s="56"/>
@@ -9417,7 +9473,7 @@
       <c r="AO32" s="56"/>
       <c r="AP32" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ32" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9496,7 +9552,9 @@
       <c r="U33" s="56">
         <v>27.05</v>
       </c>
-      <c r="V33" s="56"/>
+      <c r="V33" s="56">
+        <v>28.1</v>
+      </c>
       <c r="W33" s="56"/>
       <c r="X33" s="56"/>
       <c r="Y33" s="56"/>
@@ -9518,7 +9576,7 @@
       <c r="AO33" s="56"/>
       <c r="AP33" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ33" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9597,7 +9655,9 @@
       <c r="U34" s="56">
         <v>22.266666666666669</v>
       </c>
-      <c r="V34" s="56"/>
+      <c r="V34" s="56">
+        <v>22.6</v>
+      </c>
       <c r="W34" s="56"/>
       <c r="X34" s="56"/>
       <c r="Y34" s="56"/>
@@ -9619,7 +9679,7 @@
       <c r="AO34" s="56"/>
       <c r="AP34" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ34" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9698,7 +9758,9 @@
       <c r="U35" s="56">
         <v>25.45</v>
       </c>
-      <c r="V35" s="56"/>
+      <c r="V35" s="56">
+        <v>26.6</v>
+      </c>
       <c r="W35" s="56"/>
       <c r="X35" s="56"/>
       <c r="Y35" s="56"/>
@@ -9720,7 +9782,7 @@
       <c r="AO35" s="56"/>
       <c r="AP35" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ35" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9799,7 +9861,9 @@
       <c r="U36" s="56">
         <v>19.600000000000001</v>
       </c>
-      <c r="V36" s="56"/>
+      <c r="V36" s="56">
+        <v>19.95</v>
+      </c>
       <c r="W36" s="56"/>
       <c r="X36" s="56"/>
       <c r="Y36" s="56"/>
@@ -9821,7 +9885,7 @@
       <c r="AO36" s="56"/>
       <c r="AP36" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ36" s="71" t="str">
         <f t="shared" si="1"/>
@@ -9900,7 +9964,9 @@
       <c r="U37" s="56">
         <v>27.25</v>
       </c>
-      <c r="V37" s="56"/>
+      <c r="V37" s="56">
+        <v>28.6</v>
+      </c>
       <c r="W37" s="56"/>
       <c r="X37" s="56"/>
       <c r="Y37" s="56"/>
@@ -9922,7 +9988,7 @@
       <c r="AO37" s="56"/>
       <c r="AP37" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ37" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10001,7 +10067,9 @@
       <c r="U38" s="56">
         <v>17.3</v>
       </c>
-      <c r="V38" s="56"/>
+      <c r="V38" s="56">
+        <v>17.100000000000001</v>
+      </c>
       <c r="W38" s="56"/>
       <c r="X38" s="56"/>
       <c r="Y38" s="56"/>
@@ -10023,7 +10091,7 @@
       <c r="AO38" s="56"/>
       <c r="AP38" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ38" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10102,7 +10170,9 @@
       <c r="U39" s="56">
         <v>20.333333333333329</v>
       </c>
-      <c r="V39" s="56"/>
+      <c r="V39" s="56">
+        <v>22.066666666666659</v>
+      </c>
       <c r="W39" s="56"/>
       <c r="X39" s="56"/>
       <c r="Y39" s="56"/>
@@ -10124,7 +10194,7 @@
       <c r="AO39" s="56"/>
       <c r="AP39" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ39" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10302,7 +10372,9 @@
       <c r="U41" s="56">
         <v>19.333333333333329</v>
       </c>
-      <c r="V41" s="56"/>
+      <c r="V41" s="56">
+        <v>20.93333333333333</v>
+      </c>
       <c r="W41" s="56"/>
       <c r="X41" s="56"/>
       <c r="Y41" s="56"/>
@@ -10324,7 +10396,7 @@
       <c r="AO41" s="56"/>
       <c r="AP41" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ41" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10403,7 +10475,9 @@
       <c r="U42" s="56">
         <v>26.4</v>
       </c>
-      <c r="V42" s="56"/>
+      <c r="V42" s="56">
+        <v>27.85</v>
+      </c>
       <c r="W42" s="56"/>
       <c r="X42" s="56"/>
       <c r="Y42" s="56"/>
@@ -10425,7 +10499,7 @@
       <c r="AO42" s="56"/>
       <c r="AP42" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ42" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10504,7 +10578,9 @@
       <c r="U43" s="56">
         <v>27.4</v>
       </c>
-      <c r="V43" s="56"/>
+      <c r="V43" s="56">
+        <v>29.05</v>
+      </c>
       <c r="W43" s="56"/>
       <c r="X43" s="56"/>
       <c r="Y43" s="56"/>
@@ -10526,7 +10602,7 @@
       <c r="AO43" s="56"/>
       <c r="AP43" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ43" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10605,7 +10681,9 @@
       <c r="U44" s="56">
         <v>27.45</v>
       </c>
-      <c r="V44" s="56"/>
+      <c r="V44" s="56">
+        <v>28.324999999999999</v>
+      </c>
       <c r="W44" s="56"/>
       <c r="X44" s="56"/>
       <c r="Y44" s="56"/>
@@ -10627,7 +10705,7 @@
       <c r="AO44" s="56"/>
       <c r="AP44" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ44" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10706,7 +10784,9 @@
       <c r="U45" s="56">
         <v>27.75</v>
       </c>
-      <c r="V45" s="56"/>
+      <c r="V45" s="56">
+        <v>28.65</v>
+      </c>
       <c r="W45" s="56"/>
       <c r="X45" s="56"/>
       <c r="Y45" s="56"/>
@@ -10728,7 +10808,7 @@
       <c r="AO45" s="56"/>
       <c r="AP45" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ45" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10807,7 +10887,9 @@
       <c r="U46" s="56">
         <v>27.8</v>
       </c>
-      <c r="V46" s="56"/>
+      <c r="V46" s="56">
+        <v>29.3</v>
+      </c>
       <c r="W46" s="56"/>
       <c r="X46" s="56"/>
       <c r="Y46" s="56"/>
@@ -10829,7 +10911,7 @@
       <c r="AO46" s="56"/>
       <c r="AP46" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ46" s="71" t="str">
         <f t="shared" si="1"/>
@@ -10908,7 +10990,9 @@
       <c r="U47" s="56">
         <v>28.2</v>
       </c>
-      <c r="V47" s="56"/>
+      <c r="V47" s="56">
+        <v>30.86666666666666</v>
+      </c>
       <c r="W47" s="56"/>
       <c r="X47" s="56"/>
       <c r="Y47" s="56"/>
@@ -10930,7 +11014,7 @@
       <c r="AO47" s="56"/>
       <c r="AP47" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ47" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11167,7 +11251,9 @@
       <c r="U50" s="56">
         <v>27.75</v>
       </c>
-      <c r="V50" s="56"/>
+      <c r="V50" s="56">
+        <v>29.05</v>
+      </c>
       <c r="W50" s="56"/>
       <c r="X50" s="56"/>
       <c r="Y50" s="56"/>
@@ -11189,7 +11275,7 @@
       <c r="AO50" s="56"/>
       <c r="AP50" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ50" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11426,7 +11512,9 @@
       <c r="U53" s="56">
         <v>26.95</v>
       </c>
-      <c r="V53" s="56"/>
+      <c r="V53" s="56">
+        <v>29.35</v>
+      </c>
       <c r="W53" s="56"/>
       <c r="X53" s="56"/>
       <c r="Y53" s="56"/>
@@ -11448,7 +11536,7 @@
       <c r="AO53" s="56"/>
       <c r="AP53" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ53" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11527,7 +11615,9 @@
       <c r="U54" s="56">
         <v>28.7</v>
       </c>
-      <c r="V54" s="56"/>
+      <c r="V54" s="56">
+        <v>30.9</v>
+      </c>
       <c r="W54" s="56"/>
       <c r="X54" s="56"/>
       <c r="Y54" s="56"/>
@@ -11549,7 +11639,7 @@
       <c r="AO54" s="56"/>
       <c r="AP54" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ54" s="71" t="str">
         <f t="shared" si="1"/>
@@ -11962,7 +12052,9 @@
       <c r="U59" s="56">
         <v>29.15</v>
       </c>
-      <c r="V59" s="56"/>
+      <c r="V59" s="56">
+        <v>29.9</v>
+      </c>
       <c r="W59" s="56"/>
       <c r="X59" s="56"/>
       <c r="Y59" s="56"/>
@@ -11984,7 +12076,7 @@
       <c r="AO59" s="56"/>
       <c r="AP59" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ59" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12160,7 +12252,9 @@
       <c r="U61" s="56">
         <v>27.15</v>
       </c>
-      <c r="V61" s="56"/>
+      <c r="V61" s="56">
+        <v>26.95</v>
+      </c>
       <c r="W61" s="56"/>
       <c r="X61" s="56"/>
       <c r="Y61" s="56"/>
@@ -12182,7 +12276,7 @@
       <c r="AO61" s="56"/>
       <c r="AP61" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ61" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12619,7 +12713,9 @@
       <c r="U66" s="56">
         <v>26.3</v>
       </c>
-      <c r="V66" s="56"/>
+      <c r="V66" s="56">
+        <v>28</v>
+      </c>
       <c r="W66" s="56"/>
       <c r="X66" s="56"/>
       <c r="Y66" s="56"/>
@@ -12641,7 +12737,7 @@
       <c r="AO66" s="56"/>
       <c r="AP66" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ66" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12720,7 +12816,9 @@
       <c r="U67" s="56">
         <v>27.7</v>
       </c>
-      <c r="V67" s="56"/>
+      <c r="V67" s="56">
+        <v>27.1</v>
+      </c>
       <c r="W67" s="56"/>
       <c r="X67" s="56"/>
       <c r="Y67" s="56"/>
@@ -12742,7 +12840,7 @@
       <c r="AO67" s="56"/>
       <c r="AP67" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ67" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12821,7 +12919,9 @@
       <c r="U68" s="56">
         <v>25.5</v>
       </c>
-      <c r="V68" s="56"/>
+      <c r="V68" s="56">
+        <v>26.1</v>
+      </c>
       <c r="W68" s="56"/>
       <c r="X68" s="56"/>
       <c r="Y68" s="56"/>
@@ -12843,7 +12943,7 @@
       <c r="AO68" s="56"/>
       <c r="AP68" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ68" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12922,7 +13022,9 @@
       <c r="U69" s="56">
         <v>26.4</v>
       </c>
-      <c r="V69" s="56"/>
+      <c r="V69" s="56">
+        <v>25.2</v>
+      </c>
       <c r="W69" s="56"/>
       <c r="X69" s="56"/>
       <c r="Y69" s="56"/>
@@ -12944,7 +13046,7 @@
       <c r="AO69" s="56"/>
       <c r="AP69" s="58">
         <f t="shared" ref="AP69:AP132" si="3">COUNTIF(K69:AO69,"&gt;0")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ69" s="71" t="str">
         <f t="shared" ref="AQ69:AQ132" si="4">IF(AP69&gt;14,AVERAGE(K69:AO69),"")</f>
@@ -13023,7 +13125,9 @@
       <c r="U70" s="56">
         <v>27.8</v>
       </c>
-      <c r="V70" s="56"/>
+      <c r="V70" s="56">
+        <v>28.466666666666669</v>
+      </c>
       <c r="W70" s="56"/>
       <c r="X70" s="56"/>
       <c r="Y70" s="56"/>
@@ -13045,7 +13149,7 @@
       <c r="AO70" s="56"/>
       <c r="AP70" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ70" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13120,7 +13224,9 @@
       <c r="U71" s="56">
         <v>27.033333333333331</v>
       </c>
-      <c r="V71" s="56"/>
+      <c r="V71" s="56">
+        <v>27.63333333333334</v>
+      </c>
       <c r="W71" s="56"/>
       <c r="X71" s="56"/>
       <c r="Y71" s="56"/>
@@ -13142,7 +13248,7 @@
       <c r="AO71" s="56"/>
       <c r="AP71" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ71" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13221,7 +13327,9 @@
       <c r="U72" s="56">
         <v>25.6</v>
       </c>
-      <c r="V72" s="56"/>
+      <c r="V72" s="56">
+        <v>26.6</v>
+      </c>
       <c r="W72" s="56"/>
       <c r="X72" s="56"/>
       <c r="Y72" s="56"/>
@@ -13243,7 +13351,7 @@
       <c r="AO72" s="56"/>
       <c r="AP72" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ72" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13419,7 +13527,9 @@
       <c r="U74" s="56">
         <v>22.25</v>
       </c>
-      <c r="V74" s="56"/>
+      <c r="V74" s="56">
+        <v>21.65</v>
+      </c>
       <c r="W74" s="56"/>
       <c r="X74" s="56"/>
       <c r="Y74" s="56"/>
@@ -13441,7 +13551,7 @@
       <c r="AO74" s="56"/>
       <c r="AP74" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ74" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13520,7 +13630,9 @@
       <c r="U75" s="56">
         <v>17.666666666666671</v>
       </c>
-      <c r="V75" s="56"/>
+      <c r="V75" s="56">
+        <v>15</v>
+      </c>
       <c r="W75" s="56"/>
       <c r="X75" s="56"/>
       <c r="Y75" s="56"/>
@@ -13542,7 +13654,7 @@
       <c r="AO75" s="56"/>
       <c r="AP75" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ75" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13621,7 +13733,9 @@
       <c r="U76" s="56">
         <v>20.9</v>
       </c>
-      <c r="V76" s="56"/>
+      <c r="V76" s="56">
+        <v>20.65</v>
+      </c>
       <c r="W76" s="56"/>
       <c r="X76" s="56"/>
       <c r="Y76" s="56"/>
@@ -13643,7 +13757,7 @@
       <c r="AO76" s="56"/>
       <c r="AP76" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ76" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13722,7 +13836,9 @@
       <c r="U77" s="56">
         <v>24.2</v>
       </c>
-      <c r="V77" s="56"/>
+      <c r="V77" s="56">
+        <v>25.666666666666671</v>
+      </c>
       <c r="W77" s="56"/>
       <c r="X77" s="56"/>
       <c r="Y77" s="56"/>
@@ -13744,7 +13860,7 @@
       <c r="AO77" s="56"/>
       <c r="AP77" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ77" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13821,7 +13937,9 @@
       <c r="U78" s="56">
         <v>33.200000000000003</v>
       </c>
-      <c r="V78" s="56"/>
+      <c r="V78" s="56">
+        <v>33.4</v>
+      </c>
       <c r="W78" s="56"/>
       <c r="X78" s="56"/>
       <c r="Y78" s="56"/>
@@ -13843,7 +13961,7 @@
       <c r="AO78" s="56"/>
       <c r="AP78" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ78" s="71" t="str">
         <f t="shared" si="4"/>
@@ -13922,7 +14040,9 @@
       <c r="U79" s="56">
         <v>32.6</v>
       </c>
-      <c r="V79" s="56"/>
+      <c r="V79" s="56">
+        <v>32.799999999999997</v>
+      </c>
       <c r="W79" s="56"/>
       <c r="X79" s="56"/>
       <c r="Y79" s="56"/>
@@ -13944,7 +14064,7 @@
       <c r="AO79" s="56"/>
       <c r="AP79" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ79" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14023,7 +14143,9 @@
       <c r="U80" s="56">
         <v>21.733333333333331</v>
       </c>
-      <c r="V80" s="56"/>
+      <c r="V80" s="56">
+        <v>22.4</v>
+      </c>
       <c r="W80" s="56"/>
       <c r="X80" s="56"/>
       <c r="Y80" s="56"/>
@@ -14045,7 +14167,7 @@
       <c r="AO80" s="56"/>
       <c r="AP80" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ80" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14122,9 +14244,11 @@
         <v>26.1</v>
       </c>
       <c r="U81" s="56">
-        <v>25.933333333333341</v>
-      </c>
-      <c r="V81" s="56"/>
+        <v>25.85</v>
+      </c>
+      <c r="V81" s="56">
+        <v>25.65</v>
+      </c>
       <c r="W81" s="56"/>
       <c r="X81" s="56"/>
       <c r="Y81" s="56"/>
@@ -14146,7 +14270,7 @@
       <c r="AO81" s="56"/>
       <c r="AP81" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ81" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14223,7 +14347,9 @@
       <c r="U82" s="56">
         <v>26.533333333333331</v>
       </c>
-      <c r="V82" s="56"/>
+      <c r="V82" s="56">
+        <v>27.666666666666671</v>
+      </c>
       <c r="W82" s="56"/>
       <c r="X82" s="56"/>
       <c r="Y82" s="56"/>
@@ -14245,7 +14371,7 @@
       <c r="AO82" s="56"/>
       <c r="AP82" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ82" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14581,7 +14707,9 @@
       <c r="U86" s="56">
         <v>30.45</v>
       </c>
-      <c r="V86" s="56"/>
+      <c r="V86" s="56">
+        <v>30.6</v>
+      </c>
       <c r="W86" s="56"/>
       <c r="X86" s="56"/>
       <c r="Y86" s="56"/>
@@ -14603,7 +14731,7 @@
       <c r="AO86" s="56"/>
       <c r="AP86" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ86" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14682,7 +14810,9 @@
       <c r="U87" s="56">
         <v>30.6</v>
       </c>
-      <c r="V87" s="56"/>
+      <c r="V87" s="56">
+        <v>31.6</v>
+      </c>
       <c r="W87" s="56"/>
       <c r="X87" s="56"/>
       <c r="Y87" s="56"/>
@@ -14704,7 +14834,7 @@
       <c r="AO87" s="56"/>
       <c r="AP87" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ87" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14880,7 +15010,9 @@
         <v>32.35</v>
       </c>
       <c r="U89" s="56"/>
-      <c r="V89" s="56"/>
+      <c r="V89" s="56">
+        <v>33.099999999999987</v>
+      </c>
       <c r="W89" s="56"/>
       <c r="X89" s="56"/>
       <c r="Y89" s="56"/>
@@ -14902,7 +15034,7 @@
       <c r="AO89" s="56"/>
       <c r="AP89" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ89" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14981,7 +15113,9 @@
       <c r="U90" s="56">
         <v>32.5</v>
       </c>
-      <c r="V90" s="56"/>
+      <c r="V90" s="56">
+        <v>32.5</v>
+      </c>
       <c r="W90" s="56"/>
       <c r="X90" s="56"/>
       <c r="Y90" s="56"/>
@@ -15003,7 +15137,7 @@
       <c r="AO90" s="56"/>
       <c r="AP90" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ90" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15076,7 +15210,9 @@
       <c r="U91" s="56">
         <v>31.05</v>
       </c>
-      <c r="V91" s="56"/>
+      <c r="V91" s="56">
+        <v>34.299999999999997</v>
+      </c>
       <c r="W91" s="56"/>
       <c r="X91" s="56"/>
       <c r="Y91" s="56"/>
@@ -15098,7 +15234,7 @@
       <c r="AO91" s="56"/>
       <c r="AP91" s="58">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ91" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15177,7 +15313,9 @@
       <c r="U92" s="56">
         <v>18.55</v>
       </c>
-      <c r="V92" s="56"/>
+      <c r="V92" s="56">
+        <v>17.899999999999999</v>
+      </c>
       <c r="W92" s="56"/>
       <c r="X92" s="56"/>
       <c r="Y92" s="56"/>
@@ -15199,7 +15337,7 @@
       <c r="AO92" s="56"/>
       <c r="AP92" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ92" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15278,7 +15416,9 @@
       <c r="U93" s="56">
         <v>25.86666666666666</v>
       </c>
-      <c r="V93" s="56"/>
+      <c r="V93" s="56">
+        <v>25.733333333333331</v>
+      </c>
       <c r="W93" s="56"/>
       <c r="X93" s="56"/>
       <c r="Y93" s="56"/>
@@ -15300,7 +15440,7 @@
       <c r="AO93" s="56"/>
       <c r="AP93" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ93" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15371,9 +15511,11 @@
         <v>17.100000000000001</v>
       </c>
       <c r="U94" s="56">
-        <v>18.733333333333331</v>
-      </c>
-      <c r="V94" s="56"/>
+        <v>18.45</v>
+      </c>
+      <c r="V94" s="56">
+        <v>17.3</v>
+      </c>
       <c r="W94" s="56"/>
       <c r="X94" s="56"/>
       <c r="Y94" s="56"/>
@@ -15395,7 +15537,7 @@
       <c r="AO94" s="56"/>
       <c r="AP94" s="58">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ94" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15474,7 +15616,9 @@
       <c r="U95" s="56">
         <v>14.6</v>
       </c>
-      <c r="V95" s="56"/>
+      <c r="V95" s="56">
+        <v>16.2</v>
+      </c>
       <c r="W95" s="56"/>
       <c r="X95" s="56"/>
       <c r="Y95" s="56"/>
@@ -15496,7 +15640,7 @@
       <c r="AO95" s="56"/>
       <c r="AP95" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ95" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15654,7 +15798,9 @@
       <c r="U97" s="56">
         <v>16.666666666666661</v>
       </c>
-      <c r="V97" s="56"/>
+      <c r="V97" s="56">
+        <v>15.93333333333333</v>
+      </c>
       <c r="W97" s="56"/>
       <c r="X97" s="56"/>
       <c r="Y97" s="56"/>
@@ -15676,7 +15822,7 @@
       <c r="AO97" s="56"/>
       <c r="AP97" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ97" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15755,7 +15901,9 @@
       <c r="U98" s="56">
         <v>13.8</v>
       </c>
-      <c r="V98" s="56"/>
+      <c r="V98" s="56">
+        <v>13.2</v>
+      </c>
       <c r="W98" s="56"/>
       <c r="X98" s="56"/>
       <c r="Y98" s="56"/>
@@ -15777,7 +15925,7 @@
       <c r="AO98" s="56"/>
       <c r="AP98" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ98" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15853,8 +16001,12 @@
       <c r="T99" s="56">
         <v>15.66666666666667</v>
       </c>
-      <c r="U99" s="56"/>
-      <c r="V99" s="56"/>
+      <c r="U99" s="56">
+        <v>14.8</v>
+      </c>
+      <c r="V99" s="56">
+        <v>16.3</v>
+      </c>
       <c r="W99" s="56"/>
       <c r="X99" s="56"/>
       <c r="Y99" s="56"/>
@@ -15876,7 +16028,7 @@
       <c r="AO99" s="56"/>
       <c r="AP99" s="58">
         <f t="shared" si="3"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ99" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15955,7 +16107,9 @@
       <c r="U100" s="56">
         <v>16.600000000000001</v>
       </c>
-      <c r="V100" s="56"/>
+      <c r="V100" s="56">
+        <v>16.533333333333331</v>
+      </c>
       <c r="W100" s="56"/>
       <c r="X100" s="56"/>
       <c r="Y100" s="56"/>
@@ -15977,7 +16131,7 @@
       <c r="AO100" s="56"/>
       <c r="AP100" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ100" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16056,7 +16210,9 @@
       <c r="U101" s="56">
         <v>14.05</v>
       </c>
-      <c r="V101" s="56"/>
+      <c r="V101" s="56">
+        <v>15.6</v>
+      </c>
       <c r="W101" s="56"/>
       <c r="X101" s="56"/>
       <c r="Y101" s="56"/>
@@ -16078,7 +16234,7 @@
       <c r="AO101" s="56"/>
       <c r="AP101" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ101" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16145,7 +16301,9 @@
       <c r="U102" s="56">
         <v>13.866666666666671</v>
       </c>
-      <c r="V102" s="56"/>
+      <c r="V102" s="56">
+        <v>15.2</v>
+      </c>
       <c r="W102" s="56"/>
       <c r="X102" s="56"/>
       <c r="Y102" s="56"/>
@@ -16167,7 +16325,7 @@
       <c r="AO102" s="56"/>
       <c r="AP102" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ102" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16404,7 +16562,9 @@
       <c r="U105" s="56">
         <v>18.666666666666671</v>
       </c>
-      <c r="V105" s="56"/>
+      <c r="V105" s="56">
+        <v>19.2</v>
+      </c>
       <c r="W105" s="56"/>
       <c r="X105" s="56"/>
       <c r="Y105" s="56"/>
@@ -16426,7 +16586,7 @@
       <c r="AO105" s="56"/>
       <c r="AP105" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ105" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16665,7 +16825,9 @@
       <c r="U108" s="56">
         <v>13.75</v>
       </c>
-      <c r="V108" s="56"/>
+      <c r="V108" s="56">
+        <v>13.85</v>
+      </c>
       <c r="W108" s="56"/>
       <c r="X108" s="56"/>
       <c r="Y108" s="56"/>
@@ -16687,7 +16849,7 @@
       <c r="AO108" s="56"/>
       <c r="AP108" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ108" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16766,7 +16928,9 @@
       <c r="U109" s="56">
         <v>15.2</v>
       </c>
-      <c r="V109" s="56"/>
+      <c r="V109" s="56">
+        <v>15.85</v>
+      </c>
       <c r="W109" s="56"/>
       <c r="X109" s="56"/>
       <c r="Y109" s="56"/>
@@ -16788,7 +16952,7 @@
       <c r="AO109" s="56"/>
       <c r="AP109" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ109" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16861,7 +17025,9 @@
       <c r="U110" s="56">
         <v>18.133333333333329</v>
       </c>
-      <c r="V110" s="56"/>
+      <c r="V110" s="56">
+        <v>18.600000000000001</v>
+      </c>
       <c r="W110" s="56"/>
       <c r="X110" s="56"/>
       <c r="Y110" s="56"/>
@@ -16883,7 +17049,7 @@
       <c r="AO110" s="56"/>
       <c r="AP110" s="58">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ110" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16962,7 +17128,9 @@
       <c r="U111" s="56">
         <v>16.266666666666669</v>
       </c>
-      <c r="V111" s="56"/>
+      <c r="V111" s="56">
+        <v>17.733333333333331</v>
+      </c>
       <c r="W111" s="56"/>
       <c r="X111" s="56"/>
       <c r="Y111" s="56"/>
@@ -16984,7 +17152,7 @@
       <c r="AO111" s="56"/>
       <c r="AP111" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ111" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17063,7 +17231,9 @@
       <c r="U112" s="56">
         <v>18.533333333333331</v>
       </c>
-      <c r="V112" s="56"/>
+      <c r="V112" s="56">
+        <v>18.600000000000001</v>
+      </c>
       <c r="W112" s="56"/>
       <c r="X112" s="56"/>
       <c r="Y112" s="56"/>
@@ -17085,7 +17255,7 @@
       <c r="AO112" s="56"/>
       <c r="AP112" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ112" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17352,7 +17522,9 @@
       <c r="U115" s="56">
         <v>27.2</v>
       </c>
-      <c r="V115" s="56"/>
+      <c r="V115" s="56">
+        <v>28.85</v>
+      </c>
       <c r="W115" s="56"/>
       <c r="X115" s="56"/>
       <c r="Y115" s="56"/>
@@ -17374,7 +17546,7 @@
       <c r="AO115" s="56"/>
       <c r="AP115" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ115" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17453,7 +17625,9 @@
       <c r="U116" s="56">
         <v>19.93333333333333</v>
       </c>
-      <c r="V116" s="56"/>
+      <c r="V116" s="56">
+        <v>20</v>
+      </c>
       <c r="W116" s="56"/>
       <c r="X116" s="56"/>
       <c r="Y116" s="56"/>
@@ -17475,7 +17649,7 @@
       <c r="AO116" s="56"/>
       <c r="AP116" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ116" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17645,7 +17819,9 @@
       <c r="U118" s="56">
         <v>29.266666666666669</v>
       </c>
-      <c r="V118" s="56"/>
+      <c r="V118" s="56">
+        <v>29.4</v>
+      </c>
       <c r="W118" s="56"/>
       <c r="X118" s="56"/>
       <c r="Y118" s="56"/>
@@ -17667,7 +17843,7 @@
       <c r="AO118" s="56"/>
       <c r="AP118" s="58">
         <f t="shared" si="3"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ118" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17742,7 +17918,9 @@
       </c>
       <c r="T119" s="56"/>
       <c r="U119" s="56"/>
-      <c r="V119" s="56"/>
+      <c r="V119" s="56">
+        <v>24.066666666666659</v>
+      </c>
       <c r="W119" s="56"/>
       <c r="X119" s="56"/>
       <c r="Y119" s="56"/>
@@ -17764,7 +17942,7 @@
       <c r="AO119" s="56"/>
       <c r="AP119" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ119" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17830,8 +18008,12 @@
       <c r="T120" s="56">
         <v>27.13333333333334</v>
       </c>
-      <c r="U120" s="56"/>
-      <c r="V120" s="56"/>
+      <c r="U120" s="56">
+        <v>27.8</v>
+      </c>
+      <c r="V120" s="56">
+        <v>28.266666666666669</v>
+      </c>
       <c r="W120" s="56"/>
       <c r="X120" s="56"/>
       <c r="Y120" s="56"/>
@@ -17853,7 +18035,7 @@
       <c r="AO120" s="56"/>
       <c r="AP120" s="58">
         <f t="shared" si="3"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AQ120" s="71" t="str">
         <f t="shared" si="4"/>
@@ -18011,7 +18193,9 @@
       <c r="U122" s="56">
         <v>12.93333333333333</v>
       </c>
-      <c r="V122" s="56"/>
+      <c r="V122" s="56">
+        <v>13</v>
+      </c>
       <c r="W122" s="56"/>
       <c r="X122" s="56"/>
       <c r="Y122" s="56"/>
@@ -18033,7 +18217,7 @@
       <c r="AO122" s="56"/>
       <c r="AP122" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ122" s="71" t="str">
         <f t="shared" si="4"/>
@@ -18367,7 +18551,9 @@
       <c r="U126" s="56">
         <v>12.733333333333331</v>
       </c>
-      <c r="V126" s="56"/>
+      <c r="V126" s="56">
+        <v>11.733333333333331</v>
+      </c>
       <c r="W126" s="56"/>
       <c r="X126" s="56"/>
       <c r="Y126" s="56"/>
@@ -18389,7 +18575,7 @@
       <c r="AO126" s="56"/>
       <c r="AP126" s="58">
         <f t="shared" si="3"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ126" s="71" t="str">
         <f t="shared" si="4"/>
@@ -18705,7 +18891,9 @@
       <c r="U130" s="56">
         <v>16.033333333333331</v>
       </c>
-      <c r="V130" s="56"/>
+      <c r="V130" s="56">
+        <v>15.633333333333329</v>
+      </c>
       <c r="W130" s="56"/>
       <c r="X130" s="56"/>
       <c r="Y130" s="56"/>
@@ -18727,7 +18915,7 @@
       <c r="AO130" s="56"/>
       <c r="AP130" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ130" s="71" t="str">
         <f t="shared" si="4"/>
@@ -18806,7 +18994,9 @@
       <c r="U131" s="56">
         <v>19.2</v>
       </c>
-      <c r="V131" s="56"/>
+      <c r="V131" s="56">
+        <v>19.350000000000001</v>
+      </c>
       <c r="W131" s="56"/>
       <c r="X131" s="56"/>
       <c r="Y131" s="56"/>
@@ -18828,7 +19018,7 @@
       <c r="AO131" s="56"/>
       <c r="AP131" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ131" s="71" t="str">
         <f t="shared" si="4"/>
@@ -18986,7 +19176,9 @@
       <c r="U133" s="56">
         <v>14.2</v>
       </c>
-      <c r="V133" s="56"/>
+      <c r="V133" s="56">
+        <v>14.43333333333333</v>
+      </c>
       <c r="W133" s="56"/>
       <c r="X133" s="56"/>
       <c r="Y133" s="56"/>
@@ -19008,7 +19200,7 @@
       <c r="AO133" s="56"/>
       <c r="AP133" s="58">
         <f t="shared" ref="AP133:AP196" si="6">COUNTIF(K133:AO133,"&gt;0")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ133" s="71" t="str">
         <f t="shared" ref="AQ133:AQ196" si="7">IF(AP133&gt;14,AVERAGE(K133:AO133),"")</f>
@@ -19087,7 +19279,9 @@
       <c r="U134" s="56">
         <v>18.533333333333331</v>
       </c>
-      <c r="V134" s="56"/>
+      <c r="V134" s="56">
+        <v>17.8</v>
+      </c>
       <c r="W134" s="56"/>
       <c r="X134" s="56"/>
       <c r="Y134" s="56"/>
@@ -19109,7 +19303,7 @@
       <c r="AO134" s="56"/>
       <c r="AP134" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ134" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19188,7 +19382,9 @@
       <c r="U135" s="56">
         <v>19.100000000000001</v>
       </c>
-      <c r="V135" s="56"/>
+      <c r="V135" s="56">
+        <v>22.05</v>
+      </c>
       <c r="W135" s="56"/>
       <c r="X135" s="56"/>
       <c r="Y135" s="56"/>
@@ -19210,7 +19406,7 @@
       <c r="AO135" s="56"/>
       <c r="AP135" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ135" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19469,7 +19665,9 @@
       <c r="U138" s="56">
         <v>22.93333333333333</v>
       </c>
-      <c r="V138" s="56"/>
+      <c r="V138" s="56">
+        <v>24.86666666666666</v>
+      </c>
       <c r="W138" s="56"/>
       <c r="X138" s="56"/>
       <c r="Y138" s="56"/>
@@ -19491,7 +19689,7 @@
       <c r="AO138" s="56"/>
       <c r="AP138" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ138" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19564,7 +19762,9 @@
       <c r="U139" s="56">
         <v>15.4</v>
       </c>
-      <c r="V139" s="56"/>
+      <c r="V139" s="56">
+        <v>15.324999999999999</v>
+      </c>
       <c r="W139" s="56"/>
       <c r="X139" s="56"/>
       <c r="Y139" s="56"/>
@@ -19586,7 +19786,7 @@
       <c r="AO139" s="56"/>
       <c r="AP139" s="58">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ139" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19665,7 +19865,9 @@
       <c r="U140" s="56">
         <v>15.95</v>
       </c>
-      <c r="V140" s="56"/>
+      <c r="V140" s="56">
+        <v>17.3</v>
+      </c>
       <c r="W140" s="56"/>
       <c r="X140" s="56"/>
       <c r="Y140" s="56"/>
@@ -19687,7 +19889,7 @@
       <c r="AO140" s="56"/>
       <c r="AP140" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ140" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19766,7 +19968,9 @@
       <c r="U141" s="56">
         <v>13.46666666666667</v>
       </c>
-      <c r="V141" s="56"/>
+      <c r="V141" s="56">
+        <v>14.6</v>
+      </c>
       <c r="W141" s="56"/>
       <c r="X141" s="56"/>
       <c r="Y141" s="56"/>
@@ -19788,7 +19992,7 @@
       <c r="AO141" s="56"/>
       <c r="AP141" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ141" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19867,7 +20071,9 @@
       <c r="U142" s="56">
         <v>12.1</v>
       </c>
-      <c r="V142" s="56"/>
+      <c r="V142" s="56">
+        <v>11.75</v>
+      </c>
       <c r="W142" s="56"/>
       <c r="X142" s="56"/>
       <c r="Y142" s="56"/>
@@ -19889,7 +20095,7 @@
       <c r="AO142" s="56"/>
       <c r="AP142" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ142" s="71" t="str">
         <f t="shared" si="7"/>
@@ -19968,7 +20174,9 @@
       <c r="U143" s="56">
         <v>26.8</v>
       </c>
-      <c r="V143" s="56"/>
+      <c r="V143" s="56">
+        <v>28.466666666666669</v>
+      </c>
       <c r="W143" s="56"/>
       <c r="X143" s="56"/>
       <c r="Y143" s="56"/>
@@ -19990,7 +20198,7 @@
       <c r="AO143" s="56"/>
       <c r="AP143" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ143" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20069,7 +20277,9 @@
       <c r="U144" s="56">
         <v>15.93333333333333</v>
       </c>
-      <c r="V144" s="56"/>
+      <c r="V144" s="56">
+        <v>16.533333333333331</v>
+      </c>
       <c r="W144" s="56"/>
       <c r="X144" s="56"/>
       <c r="Y144" s="56"/>
@@ -20091,7 +20301,7 @@
       <c r="AO144" s="56"/>
       <c r="AP144" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ144" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20170,7 +20380,9 @@
       <c r="U145" s="56">
         <v>20.133333333333329</v>
       </c>
-      <c r="V145" s="56"/>
+      <c r="V145" s="56">
+        <v>20.533333333333331</v>
+      </c>
       <c r="W145" s="56"/>
       <c r="X145" s="56"/>
       <c r="Y145" s="56"/>
@@ -20192,7 +20404,7 @@
       <c r="AO145" s="56"/>
       <c r="AP145" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ145" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20271,7 +20483,9 @@
       <c r="U146" s="56">
         <v>31.06666666666667</v>
       </c>
-      <c r="V146" s="56"/>
+      <c r="V146" s="56">
+        <v>32</v>
+      </c>
       <c r="W146" s="56"/>
       <c r="X146" s="56"/>
       <c r="Y146" s="56"/>
@@ -20293,7 +20507,7 @@
       <c r="AO146" s="56"/>
       <c r="AP146" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ146" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20372,7 +20586,9 @@
       <c r="U147" s="56">
         <v>26.466666666666669</v>
       </c>
-      <c r="V147" s="56"/>
+      <c r="V147" s="56">
+        <v>27.466666666666669</v>
+      </c>
       <c r="W147" s="56"/>
       <c r="X147" s="56"/>
       <c r="Y147" s="56"/>
@@ -20394,7 +20610,7 @@
       <c r="AO147" s="56"/>
       <c r="AP147" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ147" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20473,7 +20689,9 @@
       <c r="U148" s="56">
         <v>28.733333333333331</v>
       </c>
-      <c r="V148" s="56"/>
+      <c r="V148" s="56">
+        <v>31.266666666666669</v>
+      </c>
       <c r="W148" s="56"/>
       <c r="X148" s="56"/>
       <c r="Y148" s="56"/>
@@ -20495,7 +20713,7 @@
       <c r="AO148" s="56"/>
       <c r="AP148" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ148" s="71" t="str">
         <f t="shared" si="7"/>
@@ -20574,7 +20792,9 @@
       <c r="U149" s="56">
         <v>23.4</v>
       </c>
-      <c r="V149" s="56"/>
+      <c r="V149" s="56">
+        <v>23.8</v>
+      </c>
       <c r="W149" s="56"/>
       <c r="X149" s="56"/>
       <c r="Y149" s="56"/>
@@ -20596,7 +20816,7 @@
       <c r="AO149" s="56"/>
       <c r="AP149" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ149" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21106,7 +21326,9 @@
       <c r="U155" s="56">
         <v>28.13333333333334</v>
       </c>
-      <c r="V155" s="56"/>
+      <c r="V155" s="56">
+        <v>30.066666666666659</v>
+      </c>
       <c r="W155" s="56"/>
       <c r="X155" s="56"/>
       <c r="Y155" s="56"/>
@@ -21128,7 +21350,7 @@
       <c r="AO155" s="56"/>
       <c r="AP155" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ155" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21281,7 +21503,9 @@
       <c r="T157" s="56">
         <v>31.533333333333331</v>
       </c>
-      <c r="U157" s="56"/>
+      <c r="U157" s="56">
+        <v>29.066666666666659</v>
+      </c>
       <c r="V157" s="56"/>
       <c r="W157" s="56"/>
       <c r="X157" s="56"/>
@@ -21304,7 +21528,7 @@
       <c r="AO157" s="56"/>
       <c r="AP157" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ157" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21383,7 +21607,9 @@
       <c r="U158" s="56">
         <v>31.466666666666669</v>
       </c>
-      <c r="V158" s="56"/>
+      <c r="V158" s="56">
+        <v>31.06666666666667</v>
+      </c>
       <c r="W158" s="56"/>
       <c r="X158" s="56"/>
       <c r="Y158" s="56"/>
@@ -21405,7 +21631,7 @@
       <c r="AO158" s="56"/>
       <c r="AP158" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ158" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21484,7 +21710,9 @@
       <c r="U159" s="56">
         <v>21.333333333333329</v>
       </c>
-      <c r="V159" s="56"/>
+      <c r="V159" s="56">
+        <v>21.4</v>
+      </c>
       <c r="W159" s="56"/>
       <c r="X159" s="56"/>
       <c r="Y159" s="56"/>
@@ -21506,7 +21734,7 @@
       <c r="AO159" s="56"/>
       <c r="AP159" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ159" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21583,7 +21811,9 @@
       <c r="U160" s="56">
         <v>27.266666666666669</v>
       </c>
-      <c r="V160" s="56"/>
+      <c r="V160" s="56">
+        <v>28.333333333333329</v>
+      </c>
       <c r="W160" s="56"/>
       <c r="X160" s="56"/>
       <c r="Y160" s="56"/>
@@ -21605,7 +21835,7 @@
       <c r="AO160" s="56"/>
       <c r="AP160" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ160" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21763,7 +21993,9 @@
       <c r="U162" s="56">
         <v>28</v>
       </c>
-      <c r="V162" s="56"/>
+      <c r="V162" s="56">
+        <v>28.933333333333341</v>
+      </c>
       <c r="W162" s="56"/>
       <c r="X162" s="56"/>
       <c r="Y162" s="56"/>
@@ -21785,7 +22017,7 @@
       <c r="AO162" s="56"/>
       <c r="AP162" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ162" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21864,7 +22096,9 @@
       <c r="U163" s="56">
         <v>21.533333333333331</v>
       </c>
-      <c r="V163" s="56"/>
+      <c r="V163" s="56">
+        <v>22.2</v>
+      </c>
       <c r="W163" s="56"/>
       <c r="X163" s="56"/>
       <c r="Y163" s="56"/>
@@ -21886,7 +22120,7 @@
       <c r="AO163" s="56"/>
       <c r="AP163" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ163" s="71" t="str">
         <f t="shared" si="7"/>
@@ -21965,7 +22199,9 @@
       <c r="U164" s="56">
         <v>25.2</v>
       </c>
-      <c r="V164" s="56"/>
+      <c r="V164" s="56">
+        <v>25.25</v>
+      </c>
       <c r="W164" s="56"/>
       <c r="X164" s="56"/>
       <c r="Y164" s="56"/>
@@ -21987,7 +22223,7 @@
       <c r="AO164" s="56"/>
       <c r="AP164" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ164" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22145,7 +22381,9 @@
       <c r="U166" s="56">
         <v>14.8</v>
       </c>
-      <c r="V166" s="56"/>
+      <c r="V166" s="56">
+        <v>15</v>
+      </c>
       <c r="W166" s="56"/>
       <c r="X166" s="56"/>
       <c r="Y166" s="56"/>
@@ -22167,7 +22405,7 @@
       <c r="AO166" s="56"/>
       <c r="AP166" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ166" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22246,7 +22484,9 @@
       <c r="U167" s="56">
         <v>20.93333333333333</v>
       </c>
-      <c r="V167" s="56"/>
+      <c r="V167" s="56">
+        <v>21.666666666666671</v>
+      </c>
       <c r="W167" s="56"/>
       <c r="X167" s="56"/>
       <c r="Y167" s="56"/>
@@ -22268,7 +22508,7 @@
       <c r="AO167" s="56"/>
       <c r="AP167" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ167" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22347,7 +22587,9 @@
       <c r="U168" s="56">
         <v>28.05</v>
       </c>
-      <c r="V168" s="56"/>
+      <c r="V168" s="56">
+        <v>29.1</v>
+      </c>
       <c r="W168" s="56"/>
       <c r="X168" s="56"/>
       <c r="Y168" s="56"/>
@@ -22369,7 +22611,7 @@
       <c r="AO168" s="56"/>
       <c r="AP168" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ168" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22448,7 +22690,9 @@
       <c r="U169" s="56">
         <v>8.3999999999999986</v>
       </c>
-      <c r="V169" s="56"/>
+      <c r="V169" s="56">
+        <v>10.199999999999999</v>
+      </c>
       <c r="W169" s="56"/>
       <c r="X169" s="56"/>
       <c r="Y169" s="56"/>
@@ -22470,7 +22714,7 @@
       <c r="AO169" s="56"/>
       <c r="AP169" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ169" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22549,7 +22793,9 @@
       <c r="U170" s="56">
         <v>24.2</v>
       </c>
-      <c r="V170" s="56"/>
+      <c r="V170" s="56">
+        <v>26.333333333333329</v>
+      </c>
       <c r="W170" s="56"/>
       <c r="X170" s="56"/>
       <c r="Y170" s="56"/>
@@ -22571,7 +22817,7 @@
       <c r="AO170" s="56"/>
       <c r="AP170" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ170" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22644,7 +22890,9 @@
       <c r="U171" s="56">
         <v>22.266666666666669</v>
       </c>
-      <c r="V171" s="56"/>
+      <c r="V171" s="56">
+        <v>22.733333333333331</v>
+      </c>
       <c r="W171" s="56"/>
       <c r="X171" s="56"/>
       <c r="Y171" s="56"/>
@@ -22666,7 +22914,7 @@
       <c r="AO171" s="56"/>
       <c r="AP171" s="58">
         <f t="shared" si="6"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ171" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22745,7 +22993,9 @@
       <c r="U172" s="56">
         <v>25.3</v>
       </c>
-      <c r="V172" s="56"/>
+      <c r="V172" s="56">
+        <v>26.3</v>
+      </c>
       <c r="W172" s="56"/>
       <c r="X172" s="56"/>
       <c r="Y172" s="56"/>
@@ -22767,7 +23017,7 @@
       <c r="AO172" s="56"/>
       <c r="AP172" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ172" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22846,7 +23096,9 @@
       <c r="U173" s="56">
         <v>25.05</v>
       </c>
-      <c r="V173" s="56"/>
+      <c r="V173" s="56">
+        <v>25.95</v>
+      </c>
       <c r="W173" s="56"/>
       <c r="X173" s="56"/>
       <c r="Y173" s="56"/>
@@ -22868,7 +23120,7 @@
       <c r="AO173" s="56"/>
       <c r="AP173" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ173" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23287,7 +23539,9 @@
       <c r="U178" s="56">
         <v>24.533333333333331</v>
       </c>
-      <c r="V178" s="56"/>
+      <c r="V178" s="56">
+        <v>26.333333333333329</v>
+      </c>
       <c r="W178" s="56"/>
       <c r="X178" s="56"/>
       <c r="Y178" s="56"/>
@@ -23309,7 +23563,7 @@
       <c r="AO178" s="56"/>
       <c r="AP178" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ178" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23388,7 +23642,9 @@
       <c r="U179" s="56">
         <v>18.55</v>
       </c>
-      <c r="V179" s="56"/>
+      <c r="V179" s="56">
+        <v>18.8</v>
+      </c>
       <c r="W179" s="56"/>
       <c r="X179" s="56"/>
       <c r="Y179" s="56"/>
@@ -23410,7 +23666,7 @@
       <c r="AO179" s="56"/>
       <c r="AP179" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ179" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23568,7 +23824,9 @@
       <c r="U181" s="56">
         <v>33.200000000000003</v>
       </c>
-      <c r="V181" s="56"/>
+      <c r="V181" s="56">
+        <v>33.666666666666657</v>
+      </c>
       <c r="W181" s="56"/>
       <c r="X181" s="56"/>
       <c r="Y181" s="56"/>
@@ -23590,7 +23848,7 @@
       <c r="AO181" s="56"/>
       <c r="AP181" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ181" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23827,7 +24085,9 @@
       <c r="U184" s="56">
         <v>28.533333333333331</v>
       </c>
-      <c r="V184" s="56"/>
+      <c r="V184" s="56">
+        <v>29</v>
+      </c>
       <c r="W184" s="56"/>
       <c r="X184" s="56"/>
       <c r="Y184" s="56"/>
@@ -23849,7 +24109,7 @@
       <c r="AO184" s="56"/>
       <c r="AP184" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ184" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23924,7 +24184,9 @@
       <c r="U185" s="56">
         <v>30.4</v>
       </c>
-      <c r="V185" s="56"/>
+      <c r="V185" s="56">
+        <v>32.266666666666673</v>
+      </c>
       <c r="W185" s="56"/>
       <c r="X185" s="56"/>
       <c r="Y185" s="56"/>
@@ -23946,7 +24208,7 @@
       <c r="AO185" s="56"/>
       <c r="AP185" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ185" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24181,7 +24443,9 @@
       <c r="U188" s="56">
         <v>17.533333333333331</v>
       </c>
-      <c r="V188" s="56"/>
+      <c r="V188" s="56">
+        <v>18.533333333333331</v>
+      </c>
       <c r="W188" s="56"/>
       <c r="X188" s="56"/>
       <c r="Y188" s="56"/>
@@ -24203,7 +24467,7 @@
       <c r="AO188" s="56"/>
       <c r="AP188" s="58">
         <f t="shared" si="6"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ188" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24274,7 +24538,9 @@
       <c r="U189" s="56">
         <v>32.6</v>
       </c>
-      <c r="V189" s="56"/>
+      <c r="V189" s="56">
+        <v>33.466666666666669</v>
+      </c>
       <c r="W189" s="56"/>
       <c r="X189" s="56"/>
       <c r="Y189" s="56"/>
@@ -24296,7 +24562,7 @@
       <c r="AO189" s="56"/>
       <c r="AP189" s="58">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ189" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24375,7 +24641,9 @@
       <c r="U190" s="56">
         <v>31.13333333333334</v>
       </c>
-      <c r="V190" s="56"/>
+      <c r="V190" s="56">
+        <v>32.6</v>
+      </c>
       <c r="W190" s="56"/>
       <c r="X190" s="56"/>
       <c r="Y190" s="56"/>
@@ -24397,7 +24665,7 @@
       <c r="AO190" s="56"/>
       <c r="AP190" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ190" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24476,7 +24744,9 @@
       <c r="U191" s="56">
         <v>19.45</v>
       </c>
-      <c r="V191" s="56"/>
+      <c r="V191" s="56">
+        <v>20.149999999999999</v>
+      </c>
       <c r="W191" s="56"/>
       <c r="X191" s="56"/>
       <c r="Y191" s="56"/>
@@ -24498,7 +24768,7 @@
       <c r="AO191" s="56"/>
       <c r="AP191" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ191" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24577,7 +24847,9 @@
       <c r="U192" s="56">
         <v>26.533333333333331</v>
       </c>
-      <c r="V192" s="56"/>
+      <c r="V192" s="56">
+        <v>27.6</v>
+      </c>
       <c r="W192" s="56"/>
       <c r="X192" s="56"/>
       <c r="Y192" s="56"/>
@@ -24599,7 +24871,7 @@
       <c r="AO192" s="56"/>
       <c r="AP192" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ192" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24678,7 +24950,9 @@
       <c r="U193" s="56">
         <v>29.9</v>
       </c>
-      <c r="V193" s="56"/>
+      <c r="V193" s="56">
+        <v>30.05</v>
+      </c>
       <c r="W193" s="56"/>
       <c r="X193" s="56"/>
       <c r="Y193" s="56"/>
@@ -24700,7 +24974,7 @@
       <c r="AO193" s="56"/>
       <c r="AP193" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ193" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24779,7 +25053,9 @@
       <c r="U194" s="56">
         <v>21.93333333333333</v>
       </c>
-      <c r="V194" s="56"/>
+      <c r="V194" s="56">
+        <v>23.266666666666669</v>
+      </c>
       <c r="W194" s="56"/>
       <c r="X194" s="56"/>
       <c r="Y194" s="56"/>
@@ -24801,7 +25077,7 @@
       <c r="AO194" s="56"/>
       <c r="AP194" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ194" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24876,7 +25152,9 @@
       <c r="U195" s="56">
         <v>27.533333333333331</v>
       </c>
-      <c r="V195" s="56"/>
+      <c r="V195" s="56">
+        <v>28.466666666666669</v>
+      </c>
       <c r="W195" s="56"/>
       <c r="X195" s="56"/>
       <c r="Y195" s="56"/>
@@ -24898,7 +25176,7 @@
       <c r="AO195" s="56"/>
       <c r="AP195" s="58">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ195" s="71" t="str">
         <f t="shared" si="7"/>
@@ -24977,7 +25255,9 @@
       <c r="U196" s="56">
         <v>23.2</v>
       </c>
-      <c r="V196" s="56"/>
+      <c r="V196" s="56">
+        <v>23.6</v>
+      </c>
       <c r="W196" s="56"/>
       <c r="X196" s="56"/>
       <c r="Y196" s="56"/>
@@ -24999,7 +25279,7 @@
       <c r="AO196" s="56"/>
       <c r="AP196" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ196" s="71" t="str">
         <f t="shared" si="7"/>
@@ -25078,7 +25358,9 @@
       <c r="U197" s="56">
         <v>27.733333333333331</v>
       </c>
-      <c r="V197" s="56"/>
+      <c r="V197" s="56">
+        <v>28.466666666666669</v>
+      </c>
       <c r="W197" s="56"/>
       <c r="X197" s="56"/>
       <c r="Y197" s="56"/>
@@ -25100,7 +25382,7 @@
       <c r="AO197" s="56"/>
       <c r="AP197" s="58">
         <f t="shared" ref="AP197:AP260" si="9">COUNTIF(K197:AO197,"&gt;0")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ197" s="71" t="str">
         <f t="shared" ref="AQ197:AQ260" si="10">IF(AP197&gt;14,AVERAGE(K197:AO197),"")</f>
@@ -25179,7 +25461,9 @@
       <c r="U198" s="56">
         <v>22.3</v>
       </c>
-      <c r="V198" s="56"/>
+      <c r="V198" s="56">
+        <v>22.25</v>
+      </c>
       <c r="W198" s="56"/>
       <c r="X198" s="56"/>
       <c r="Y198" s="56"/>
@@ -25201,7 +25485,7 @@
       <c r="AO198" s="56"/>
       <c r="AP198" s="58">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ198" s="71" t="str">
         <f t="shared" si="10"/>
@@ -25280,7 +25564,9 @@
       <c r="U199" s="56">
         <v>16.666666666666671</v>
       </c>
-      <c r="V199" s="56"/>
+      <c r="V199" s="56">
+        <v>17</v>
+      </c>
       <c r="W199" s="56"/>
       <c r="X199" s="56"/>
       <c r="Y199" s="56"/>
@@ -25302,7 +25588,7 @@
       <c r="AO199" s="56"/>
       <c r="AP199" s="58">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ199" s="71" t="str">
         <f t="shared" si="10"/>
@@ -25379,7 +25665,9 @@
       <c r="U200" s="56">
         <v>15</v>
       </c>
-      <c r="V200" s="56"/>
+      <c r="V200" s="56">
+        <v>14.2</v>
+      </c>
       <c r="W200" s="56"/>
       <c r="X200" s="56"/>
       <c r="Y200" s="56"/>
@@ -25401,7 +25689,7 @@
       <c r="AO200" s="56"/>
       <c r="AP200" s="58">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ200" s="71" t="str">
         <f t="shared" si="10"/>
@@ -25480,7 +25768,9 @@
       <c r="U201" s="56">
         <v>28.8</v>
       </c>
-      <c r="V201" s="56"/>
+      <c r="V201" s="56">
+        <v>29.75</v>
+      </c>
       <c r="W201" s="56"/>
       <c r="X201" s="56"/>
       <c r="Y201" s="56"/>
@@ -25502,7 +25792,7 @@
       <c r="AO201" s="56"/>
       <c r="AP201" s="58">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ201" s="71" t="str">
         <f t="shared" si="10"/>
@@ -25579,7 +25869,9 @@
       <c r="U202" s="56">
         <v>13.3</v>
       </c>
-      <c r="V202" s="56"/>
+      <c r="V202" s="56">
+        <v>13.6</v>
+      </c>
       <c r="W202" s="56"/>
       <c r="X202" s="56"/>
       <c r="Y202" s="56"/>
@@ -25601,7 +25893,7 @@
       <c r="AO202" s="56"/>
       <c r="AP202" s="58">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ202" s="71" t="str">
         <f t="shared" si="10"/>
@@ -25857,8 +26149,12 @@
       <c r="T205" s="56">
         <v>15.75</v>
       </c>
-      <c r="U205" s="56"/>
-      <c r="V205" s="56"/>
+      <c r="U205" s="56">
+        <v>15.25</v>
+      </c>
+      <c r="V205" s="56">
+        <v>15.6</v>
+      </c>
       <c r="W205" s="56"/>
       <c r="X205" s="56"/>
       <c r="Y205" s="56"/>
@@ -25880,7 +26176,7 @@
       <c r="AO205" s="56"/>
       <c r="AP205" s="58">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ205" s="71" t="str">
         <f t="shared" si="10"/>
@@ -26157,7 +26453,9 @@
       <c r="U208" s="56">
         <v>13.5</v>
       </c>
-      <c r="V208" s="56"/>
+      <c r="V208" s="56">
+        <v>14</v>
+      </c>
       <c r="W208" s="56"/>
       <c r="X208" s="56"/>
       <c r="Y208" s="56"/>
@@ -26179,7 +26477,7 @@
       <c r="AO208" s="56"/>
       <c r="AP208" s="58">
         <f t="shared" si="9"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ208" s="71" t="str">
         <f t="shared" si="10"/>
@@ -26258,7 +26556,9 @@
       <c r="U209" s="56">
         <v>10.55</v>
       </c>
-      <c r="V209" s="56"/>
+      <c r="V209" s="56">
+        <v>10.8</v>
+      </c>
       <c r="W209" s="56"/>
       <c r="X209" s="56"/>
       <c r="Y209" s="56"/>
@@ -26280,7 +26580,7 @@
       <c r="AO209" s="56"/>
       <c r="AP209" s="58">
         <f t="shared" si="9"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ209" s="71" t="str">
         <f t="shared" si="10"/>
@@ -26354,7 +26654,9 @@
       <c r="T210" s="56">
         <v>17.2</v>
       </c>
-      <c r="U210" s="56"/>
+      <c r="U210" s="56">
+        <v>16.350000000000001</v>
+      </c>
       <c r="V210" s="56"/>
       <c r="W210" s="56"/>
       <c r="X210" s="56"/>
@@ -26377,7 +26679,7 @@
       <c r="AO210" s="56"/>
       <c r="AP210" s="58">
         <f t="shared" si="9"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ210" s="71" t="str">
         <f t="shared" si="10"/>
